--- a/docs/referencia/Perfecting_ROI_Calculator_Template.xlsx
+++ b/docs/referencia/Perfecting_ROI_Calculator_Template.xlsx
@@ -4632,11 +4632,11 @@
     <row r="31" ht="19.5" customHeight="1" s="91">
       <c r="B31" s="120" t="inlineStr">
         <is>
-          <t>Tier 2 — 263 a 573 h</t>
+          <t>Tier 2 — 263 a 656 h</t>
         </is>
       </c>
       <c r="C31" s="124" t="n">
-        <v>573</v>
+        <v>656</v>
       </c>
       <c r="D31" s="122" t="n"/>
       <c r="E31" s="127" t="n">
@@ -4648,7 +4648,7 @@
     <row r="32" ht="19.5" customHeight="1" s="91">
       <c r="B32" s="120" t="inlineStr">
         <is>
-          <t>Tier 3 — 574 a 1.243 h</t>
+          <t>Tier 3 — 657 a 1.243 h</t>
         </is>
       </c>
       <c r="C32" s="124" t="n">
@@ -7652,7 +7652,7 @@
     <row r="52" ht="19.5" customHeight="1" s="91">
       <c r="B52" s="120" t="inlineStr">
         <is>
-          <t>Novos vendedores/ano</t>
+          <t>Ciclo de vendas atual (dias)</t>
         </is>
       </c>
       <c r="C52" s="152">
@@ -7699,7 +7699,7 @@
     <row r="53" ht="19.5" customHeight="1" s="91">
       <c r="B53" s="120" t="inlineStr">
         <is>
-          <t>Meses efetivos de rampa</t>
+          <t>Ciclo longo? (≥ 7 dias)</t>
         </is>
       </c>
       <c r="C53" s="149">
@@ -9394,7 +9394,7 @@
     <row r="18" ht="19.5" customHeight="1" s="91">
       <c r="B18" s="120" t="inlineStr">
         <is>
-          <t>Tier 2 (263-573h)</t>
+          <t>Tier 2 (263-656h)</t>
         </is>
       </c>
       <c r="C18" s="150">
@@ -9414,7 +9414,7 @@
     <row r="19" ht="19.5" customHeight="1" s="91">
       <c r="B19" s="120" t="inlineStr">
         <is>
-          <t>Tier 3 (574-1243h)</t>
+          <t>Tier 3 (657-1243h)</t>
         </is>
       </c>
       <c r="C19" s="150">
